--- a/template_golden.xlsx
+++ b/template_golden.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WMCIntern\Downloads\Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74D8633A-1B74-4958-A784-5F8B57838CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{543ED132-838C-40E2-8397-4F9CDDDC08B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="380" windowWidth="10550" windowHeight="9590" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5061,7 +5061,7 @@
         <v>16</v>
       </c>
       <c r="P41" s="1">
-        <v>1500000</v>
+        <v>150000</v>
       </c>
       <c r="Q41" s="1">
         <v>0</v>
